--- a/output/graficos_regionales/plot_regional_serie_i_ingr_s_2018_antofagasta.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_s_2018_antofagasta.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:35</t>
+    <t xml:space="preserve">2026-10-05 01:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>999708.62</v>
+        <v>999708.63</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>795057.75</v>
@@ -502,7 +502,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1042348.12</v>
+        <v>1042348.13</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>829060.94</v>
@@ -535,7 +535,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1086974.12</v>
+        <v>1086974.13</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>878312.06</v>
@@ -568,7 +568,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1176690.12</v>
+        <v>1176690.13</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>976086</v>
@@ -604,7 +604,7 @@
         <v>1391420</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1163774.62</v>
+        <v>1163774.63</v>
       </c>
     </row>
     <row r="13">
@@ -634,7 +634,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1542401.12</v>
+        <v>1542401.13</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>1298591</v>
